--- a/DualCore/PinAssignment.xlsx
+++ b/DualCore/PinAssignment.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GIT-Repos\RaspiPico\DualCore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F970B347-ACC9-49F4-8E42-8EE74117BC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A3EF45-33B9-44C9-B787-7CCB884354E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="1020" windowWidth="29210" windowHeight="17610" xr2:uid="{30121305-4F5C-4C09-A6BD-A9BC175C3B4F}"/>
+    <workbookView xWindow="1700" yWindow="1700" windowWidth="29210" windowHeight="17610" xr2:uid="{30121305-4F5C-4C09-A6BD-A9BC175C3B4F}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="87">
   <si>
     <t>RP2040 Zero PinOut und Belegung</t>
   </si>
@@ -588,6 +589,30 @@
   </si>
   <si>
     <t>Internally connected to WS2812 RGB  LED</t>
+  </si>
+  <si>
+    <t>Core1-Uart</t>
+  </si>
+  <si>
+    <t>Core0-Uart</t>
+  </si>
+  <si>
+    <t>GC9A01 SCK</t>
+  </si>
+  <si>
+    <t>GC9A01 SDI</t>
+  </si>
+  <si>
+    <t>GC9A01 nCS</t>
+  </si>
+  <si>
+    <t>GC9A01 Reset</t>
+  </si>
+  <si>
+    <t>GC9A01 D/C</t>
+  </si>
+  <si>
+    <t>I2C interface</t>
   </si>
 </sst>
 </file>
@@ -718,7 +743,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -733,35 +758,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1113,13 +1119,12 @@
   <dimension ref="B3:M37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="3.453125" customWidth="1"/>
-    <col min="3" max="3" width="3.453125" style="6" customWidth="1"/>
+    <col min="2" max="3" width="3.453125" customWidth="1"/>
     <col min="12" max="12" width="3.36328125" customWidth="1"/>
     <col min="13" max="13" width="41.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
@@ -1127,25 +1132,25 @@
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
     </row>
-    <row r="4" spans="2:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" spans="2:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C5" s="6" t="s">
+    <row r="5" spans="2:13" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="10" t="s">
         <v>25</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -1163,15 +1168,18 @@
       <c r="K6" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="M6" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D7" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="11" t="s">
         <v>32</v>
       </c>
       <c r="G7" s="3" t="s">
@@ -1190,7 +1198,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D8" s="1" t="s">
         <v>3</v>
       </c>
@@ -1200,7 +1208,7 @@
       <c r="F8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="10" t="s">
         <v>37</v>
       </c>
       <c r="H8" s="1" t="s">
@@ -1215,8 +1223,11 @@
       <c r="K8" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="M8" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D9" s="2" t="s">
         <v>4</v>
       </c>
@@ -1226,7 +1237,7 @@
       <c r="F9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="12" t="s">
         <v>41</v>
       </c>
       <c r="H9" s="2" t="s">
@@ -1242,14 +1253,14 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="10" t="s">
         <v>43</v>
       </c>
       <c r="G10" s="1" t="s">
@@ -1267,15 +1278,18 @@
       <c r="K10" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="M10" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="11" t="s">
         <v>45</v>
       </c>
       <c r="G11" s="3" t="s">
@@ -1294,7 +1308,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1320,7 +1334,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D13" s="2" t="s">
         <v>8</v>
       </c>
@@ -1346,7 +1360,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1362,7 +1376,7 @@
       <c r="H14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I14" s="17" t="s">
+      <c r="I14" s="10" t="s">
         <v>28</v>
       </c>
       <c r="J14" s="1" t="s">
@@ -1371,8 +1385,11 @@
       <c r="K14" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="M14" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D15" s="2" t="s">
         <v>10</v>
       </c>
@@ -1388,7 +1405,7 @@
       <c r="H15" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I15" s="19" t="s">
+      <c r="I15" s="12" t="s">
         <v>28</v>
       </c>
       <c r="J15" s="3" t="s">
@@ -1397,18 +1414,21 @@
       <c r="K15" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="M15" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D16" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="10" t="s">
         <v>55</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="17" t="s">
+      <c r="G16" s="1" t="s">
         <v>37</v>
       </c>
       <c r="H16" s="1" t="s">
@@ -1422,19 +1442,22 @@
       </c>
       <c r="K16" s="1" t="s">
         <v>30</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="3:13" x14ac:dyDescent="0.35">
       <c r="D17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="10" t="s">
         <v>57</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="2" t="s">
         <v>41</v>
       </c>
       <c r="H17" s="2" t="s">
@@ -1448,6 +1471,9 @@
       </c>
       <c r="K17" s="3" t="s">
         <v>30</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="3:13" x14ac:dyDescent="0.35">
@@ -1466,7 +1492,7 @@
       <c r="H18" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I18" s="17" t="s">
+      <c r="I18" s="10" t="s">
         <v>28</v>
       </c>
       <c r="J18" s="1" t="s">
@@ -1474,6 +1500,9 @@
       </c>
       <c r="K18" s="1" t="s">
         <v>30</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="3:13" x14ac:dyDescent="0.35">
@@ -1555,7 +1584,7 @@
       </c>
     </row>
     <row r="22" spans="3:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E22" s="4" t="s">
@@ -1573,122 +1602,122 @@
       <c r="I22" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="J22" s="12" t="s">
+      <c r="J22" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="M22" s="16" t="s">
+      <c r="M22" s="9" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="23" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="G23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="H23" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I23" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K23" s="7" t="s">
+      <c r="I23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="24" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="I24" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J24" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="K24" s="11" t="s">
+      <c r="I24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="25" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="G25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H25" s="7" t="s">
+      <c r="H25" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I25" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K25" s="7" t="s">
+      <c r="I25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K25" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="26" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G26" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H26" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="I26" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J26" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="K26" s="11" t="s">
+      <c r="I26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="28" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C28" s="6" t="s">
+      <c r="C28" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1696,25 +1725,25 @@
       <c r="D29" t="s">
         <v>65</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G29" s="15" t="s">
+      <c r="G29" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H29" s="14" t="s">
+      <c r="H29" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I29" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="J29" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K29" s="15" t="s">
+      <c r="I29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1722,25 +1751,25 @@
       <c r="D30" t="s">
         <v>66</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E30" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F30" s="13" t="s">
+      <c r="F30" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="G30" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H30" s="13" t="s">
+      <c r="H30" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J30" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="K30" s="13" t="s">
+      <c r="I30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K30" s="1" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1748,25 +1777,25 @@
       <c r="D31" t="s">
         <v>67</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G31" s="15" t="s">
+      <c r="G31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H31" s="14" t="s">
+      <c r="H31" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I31" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="J31" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K31" s="15" t="s">
+      <c r="I31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K31" s="3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1774,25 +1803,25 @@
       <c r="D32" t="s">
         <v>68</v>
       </c>
-      <c r="E32" s="13" t="s">
+      <c r="E32" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F32" s="13" t="s">
+      <c r="F32" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="G32" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H32" s="13" t="s">
+      <c r="H32" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I32" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J32" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="K32" s="13" t="s">
+      <c r="I32" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1800,25 +1829,25 @@
       <c r="D33" t="s">
         <v>69</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="15" t="s">
+      <c r="G33" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H33" s="14" t="s">
+      <c r="H33" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I33" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="J33" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K33" s="15" t="s">
+      <c r="I33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K33" s="3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1826,25 +1855,25 @@
       <c r="D34" t="s">
         <v>70</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="E34" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F34" s="13" t="s">
+      <c r="F34" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G34" s="13" t="s">
+      <c r="G34" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H34" s="13" t="s">
+      <c r="H34" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I34" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J34" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="K34" s="13" t="s">
+      <c r="I34" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K34" s="1" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1852,25 +1881,25 @@
       <c r="D35" t="s">
         <v>71</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G35" s="15" t="s">
+      <c r="G35" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H35" s="14" t="s">
+      <c r="H35" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I35" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="J35" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K35" s="15" t="s">
+      <c r="I35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K35" s="3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1878,25 +1907,25 @@
       <c r="D36" t="s">
         <v>72</v>
       </c>
-      <c r="E36" s="13" t="s">
+      <c r="E36" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F36" s="13" t="s">
+      <c r="F36" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G36" s="13" t="s">
+      <c r="G36" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H36" s="13" t="s">
+      <c r="H36" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I36" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J36" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="K36" s="13" t="s">
+      <c r="I36" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K36" s="1" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1904,25 +1933,25 @@
       <c r="D37" t="s">
         <v>73</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F37" s="14" t="s">
+      <c r="F37" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G37" s="15" t="s">
+      <c r="G37" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H37" s="14" t="s">
+      <c r="H37" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I37" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="J37" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K37" s="15" t="s">
+      <c r="I37" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K37" s="3" t="s">
         <v>30</v>
       </c>
     </row>
